--- a/tests/wson-test.xlsx
+++ b/tests/wson-test.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">!</t>
   </si>
   <si>
-    <t xml:space="preserve">table &gt;&gt;</t>
+    <t xml:space="preserve">table &lt;&lt;</t>
   </si>
   <si>
     <t xml:space="preserve">id</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Value3</t>
   </si>
   <si>
-    <t xml:space="preserve">+&gt;</t>
+    <t xml:space="preserve">&gt;&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Id</t>
@@ -320,7 +320,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,11 +340,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,37 +429,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -603,9 +603,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.01"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -739,10 +739,10 @@
       <c r="H14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -765,10 +765,10 @@
       <c r="H15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="0" t="s">
+      <c r="I15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -779,7 +779,7 @@
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -790,7 +790,7 @@
       <c r="C18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -801,7 +801,7 @@
       <c r="C19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -821,12 +821,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D15"/>
+  <dimension ref="B1:D15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.36"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="7" t="s">
         <v>44</v>
@@ -834,7 +835,7 @@
       <c r="C2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -842,15 +843,15 @@
       <c r="C3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -858,10 +859,12 @@
       <c r="C5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="8" t="b">
+      <c r="D5" s="8" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
         <v>44</v>
@@ -869,7 +872,7 @@
       <c r="C7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -877,15 +880,15 @@
       <c r="C8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -893,10 +896,12 @@
       <c r="C10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="8" t="b">
+      <c r="D10" s="8" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
         <v>44</v>
@@ -904,7 +909,7 @@
       <c r="C12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -912,7 +917,7 @@
       <c r="C13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -920,7 +925,7 @@
       <c r="C14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -928,7 +933,8 @@
       <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="8" t="b">
+      <c r="D15" s="8" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>

--- a/tests/wson-test.xlsx
+++ b/tests/wson-test.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FullTest" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="TopLevelArray" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t xml:space="preserve">&gt;</t>
   </si>
@@ -186,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">charlie@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test</t>
   </si>
 </sst>
 </file>
@@ -952,4 +956,34 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/tests/wson-test.xlsx
+++ b/tests/wson-test.xlsx
@@ -5,12 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="FullTest" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="TopLevelArray" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="OnlyOne" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="InlineBlocks" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="TopLevelSimpleArray" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t xml:space="preserve">&gt;</t>
   </si>
@@ -69,7 +71,7 @@
     <t xml:space="preserve">in sub obj 2 !</t>
   </si>
   <si>
-    <t xml:space="preserve">[inline] &lt;</t>
+    <t xml:space="preserve">inline &lt;</t>
   </si>
   <si>
     <t xml:space="preserve">array</t>
@@ -84,6 +86,9 @@
     <t xml:space="preserve">!</t>
   </si>
   <si>
+    <t xml:space="preserve">inline-colors &lt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">table &lt;&lt;</t>
   </si>
   <si>
@@ -141,7 +146,7 @@
     <t xml:space="preserve">!!</t>
   </si>
   <si>
-    <t xml:space="preserve">[inline] &gt;</t>
+    <t xml:space="preserve">[appender] &gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Key</t>
@@ -156,6 +161,18 @@
     <t xml:space="preserve">Value3</t>
   </si>
   <si>
+    <t xml:space="preserve">inline-object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..{Inline: Object, With: [1, 2, 3],}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inline-array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..[Some, Values]</t>
+  </si>
+  <si>
     <t xml:space="preserve">&gt;&gt;</t>
   </si>
   <si>
@@ -190,6 +207,15 @@
   </si>
   <si>
     <t xml:space="preserve">Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..[interpolate, [linear], [zoom], 4, 1, 10, 2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..{obj: [1, 2, 3], other: value, hey: false}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;</t>
   </si>
 </sst>
 </file>
@@ -315,7 +341,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -348,7 +374,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -362,6 +396,24 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Prop" xfId="20"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -602,103 +654,101 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:J19"/>
+  <dimension ref="B2:K22"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.01"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
@@ -709,7 +759,7 @@
         <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>24</v>
@@ -717,17 +767,17 @@
       <c r="H13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>24</v>
+      <c r="I13" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="K13" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
@@ -749,11 +799,11 @@
       <c r="J14" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="K14" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D15" s="1" t="s">
         <v>35</v>
       </c>
@@ -763,50 +813,69 @@
       <c r="F15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>38</v>
+      <c r="K15" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="E17" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>42</v>
+      <c r="D18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>43</v>
+      <c r="D19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -834,10 +903,10 @@
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -845,25 +914,25 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -871,10 +940,10 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>2</v>
@@ -882,25 +951,25 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -908,10 +977,10 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>3</v>
@@ -919,25 +988,25 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -968,13 +1037,97 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>55</v>
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(NOT(ISBLANK(E2)),NOT(ISBLANK(D2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/tests/wson-test.xlsx
+++ b/tests/wson-test.xlsx
@@ -341,7 +341,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -374,15 +374,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -411,7 +407,6 @@
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -657,7 +652,7 @@
   <dimension ref="B2:K22"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.77"/>
@@ -863,7 +858,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -871,7 +866,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -932,7 +927,7 @@
       <c r="C5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -969,7 +964,7 @@
       <c r="C10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1006,7 +1001,7 @@
       <c r="C15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -1032,17 +1027,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D2"/>
+  <dimension ref="B1:D2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1062,28 +1058,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D3"/>
+  <dimension ref="B1:D3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1108,25 +1105,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D3"/>
+  <dimension ref="B1:D3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>38</v>
       </c>
     </row>
